--- a/important_mails_2026-04-04.xlsx
+++ b/important_mails_2026-04-04.xlsx
@@ -1008,7 +1008,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1023,121 +1023,21 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -1147,39 +1047,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -1189,39 +1089,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -1251,39 +1151,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1301,39 +1201,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1350,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1398,39 +1298,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -1459,39 +1359,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -1512,39 +1412,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1559,39 +1459,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1609,39 +1509,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1671,40 +1571,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1720,39 +1620,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1772,39 +1672,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1830,39 +1730,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1878,39 +1778,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1931,39 +1831,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1977,40 +1877,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2026,39 +1926,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2078,39 +1978,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2124,39 +2024,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2176,39 +2076,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2229,39 +2129,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2281,39 +2181,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2330,39 +2230,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2379,39 +2279,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2426,39 +2326,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2482,39 +2382,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2528,39 +2428,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2577,39 +2477,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2629,39 +2529,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2675,6 +2575,106 @@
  ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
 Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
 Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-04-04.xlsx
+++ b/important_mails_2026-04-04.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1415,7 +1415,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1430,68 +1430,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
+          <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pagamento elaborato con successo</t>
+          <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 03/28/26 15:19 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 217,83.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1509,39 +1462,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1571,40 +1524,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1620,39 +1573,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1672,39 +1625,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1730,39 +1683,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1778,39 +1731,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1831,39 +1784,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1877,40 +1830,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1926,39 +1879,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1978,39 +1931,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2024,39 +1977,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2076,39 +2029,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2129,39 +2082,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2181,39 +2134,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2230,39 +2183,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2279,39 +2232,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2326,39 +2279,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2382,39 +2335,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2428,39 +2381,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2477,39 +2430,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2529,88 +2482,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 03/05/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 93,03.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxit</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2628,39 +2532,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2678,39 +2582,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -2725,39 +2629,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2775,39 +2679,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2825,39 +2729,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2875,39 +2779,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2922,39 +2826,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2969,39 +2873,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3016,39 +2920,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3067,40 +2971,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3119,39 +3023,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3161,39 +3065,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3211,39 +3115,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3259,39 +3163,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3310,39 +3214,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3360,39 +3264,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3414,39 +3318,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3469,39 +3373,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3520,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3571,39 +3475,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3623,39 +3527,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3675,39 +3579,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3725,39 +3629,89 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Rispondi ai requisiti di conformità per le tue offerte</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>96
+Azione richiesta: Informazioni importanti sulle sue offerte
+ La contattiamo perché ha pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità.
+ Le offerte dei prodotti sono prive dei documenti di conformità obbligatori
+ Buongiorno,
+ ti contattiamo perché hai pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità. Clicca su Visualizza requisiti di conformità qui sotto per accedere all'elenco dei prodotti interessati e inviare i documenti di conformità richiesti. Se non invierai i documenti entro il termine indicato per ciascun prodotto, le offerte di tali prodotti potrebbero essere rimosse.
+ Visualizza requisiti di conformità
+ La tabella seguente contiene un campione delle offerte interessate. Clicca su Visualizza requisiti di conformità per accedere all'elenco completo.
+ SKU ASIN Stato delle offerte WHEUSGMH81901 B0DD7R3PPG A rischio di rimozione
+ Perché succede questo?
+L'aderenza ai requisiti contribuisce a garantire che i prodotti siano conformi alle leggi locali e non rappresentino un rischio per i clienti.
+ Come faccio a continuare a vendere i prodotti interessati?
+Clicca su Visualizza requisiti di conformità per ottenere ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3775,89 +3729,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Rispondi ai requisiti di conformità per le tue offerte</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>96
-Azione richiesta: Informazioni importanti sulle sue offerte
- La contattiamo perché ha pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità.
- Le offerte dei prodotti sono prive dei documenti di conformità obbligatori
- Buongiorno,
- ti contattiamo perché hai pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità. Clicca su Visualizza requisiti di conformità qui sotto per accedere all'elenco dei prodotti interessati e inviare i documenti di conformità richiesti. Se non invierai i documenti entro il termine indicato per ciascun prodotto, le offerte di tali prodotti potrebbero essere rimosse.
- Visualizza requisiti di conformità
- La tabella seguente contiene un campione delle offerte interessate. Clicca su Visualizza requisiti di conformità per accedere all'elenco completo.
- SKU ASIN Stato delle offerte WHEUSGMH81901 B0DD7R3PPG A rischio di rimozione
- Perché succede questo?
-L'aderenza ai requisiti contribuisce a garantire che i prodotti siano conformi alle leggi locali e non rappresentino un rischio per i clienti.
- Come faccio a continuare a vendere i prodotti interessati?
-Clicca su Visualizza requisiti di conformità per ottenere ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3876,39 +3780,86 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 03/28/26 15:19 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 217,83.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3922,40 +3873,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3971,39 +3922,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4019,39 +3970,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -4067,39 +4018,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4115,40 +4066,40 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4164,39 +4115,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4214,39 +4165,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -4262,39 +4213,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4309,39 +4260,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -4356,39 +4307,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4409,40 +4360,40 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -4457,39 +4408,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -4510,39 +4461,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4575,39 +4526,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4623,39 +4574,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4671,39 +4622,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4721,39 +4672,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4770,39 +4721,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4826,39 +4777,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4873,39 +4824,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4921,39 +4872,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4970,40 +4921,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5019,39 +4970,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -5071,39 +5022,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5119,40 +5070,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5168,39 +5119,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5217,39 +5168,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5268,39 +5219,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5318,39 +5269,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -5362,39 +5313,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5406,39 +5357,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5450,39 +5401,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5494,39 +5445,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5538,39 +5489,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5582,39 +5533,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5626,39 +5577,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5670,39 +5621,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5720,39 +5671,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5795,39 +5746,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5844,40 +5795,40 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5895,39 +5846,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5945,39 +5896,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5989,39 +5940,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6033,39 +5984,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6084,39 +6035,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6128,39 +6079,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6172,39 +6123,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6216,39 +6167,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6260,39 +6211,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6304,39 +6255,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6348,39 +6299,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6392,39 +6343,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6436,39 +6387,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6480,40 +6431,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6532,39 +6483,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6576,40 +6527,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6621,39 +6572,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6665,39 +6616,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6716,39 +6667,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6760,39 +6711,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6811,39 +6762,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6855,39 +6806,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6903,40 +6854,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6954,39 +6905,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7004,39 +6955,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -7052,39 +7003,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -7102,39 +7053,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -7175,39 +7126,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7225,40 +7176,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7276,39 +7227,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7325,39 +7276,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7375,39 +7326,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7428,39 +7379,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7483,39 +7434,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7536,39 +7487,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7592,39 +7543,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7647,39 +7598,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7702,39 +7653,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7756,39 +7707,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7811,39 +7762,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7866,39 +7817,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7914,39 +7865,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7962,40 +7913,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8014,40 +7965,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8065,39 +8016,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8111,39 +8062,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8161,39 +8112,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8210,39 +8161,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8260,40 +8211,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8312,39 +8263,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
